--- a/data/trans_orig/IP22D5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22D5_2023-Habitat-trans_orig.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>16021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>94306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22D5_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10748</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10225</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19594</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16021</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13929</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9950</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14803</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>67,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17222</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>42</t>
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4411</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>32,79%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4749</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11036</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9579</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11220</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9296</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>95,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>78,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11634</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9158</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12175</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>75,22%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11305</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9211</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11701</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>78,72%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>839</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11042</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8138</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>12755</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,27 +2163,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3825</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4183</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4487</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -2314,107 +2314,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,102 +2549,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>41616</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>37864</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>51507</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>47283</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>52863</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>88504</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>84107</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>90584</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>96,69%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>98249</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>94306</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>100353</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2770,107 +2770,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
